--- a/06-sizing-cost/worksheet/sizing-workbook.xlsx
+++ b/06-sizing-cost/worksheet/sizing-workbook.xlsx
@@ -3094,10 +3094,64 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">아니오</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예 또는 아니오</t>
+    <t xml:space="preserve">예</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">예 또는 아니오</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">기본 성능 작동점이 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NIM </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">측정값이라 기본값은 예</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">클러스터 배치</t>
@@ -9957,7 +10011,7 @@
       </c>
       <c r="C5" s="23" t="n">
         <f aca="false">IF(OR(입력!$C$39="vGPU",입력!$C$40="예"),산정!C34,0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>85</v>
@@ -10015,7 +10069,7 @@
       </c>
       <c r="C10" s="23" t="n">
         <f aca="false">C5</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="35" t="str">
